--- a/output/pdf_financials_xlsx/MG.xlsx
+++ b/output/pdf_financials_xlsx/MG.xlsx
@@ -8556,31 +8556,31 @@
         <v>-354</v>
       </c>
       <c r="K126" s="3" t="n">
-        <v>-385</v>
+        <v>-391</v>
       </c>
       <c r="L126" s="3" t="n">
-        <v>-400</v>
+        <v>-438</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>-448</v>
+        <v>-517</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>-449</v>
+        <v>-471</v>
       </c>
       <c r="O126" s="3" t="n">
-        <v>-514</v>
+        <v>-563</v>
       </c>
       <c r="P126" s="3" t="n">
-        <v>-514</v>
+        <v>-46</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>0</v>
+        <v>-74</v>
       </c>
       <c r="R126" s="3" t="n">
-        <v>0</v>
+        <v>-46</v>
       </c>
       <c r="S126" s="3" t="n">
-        <v>0</v>
+        <v>-59</v>
       </c>
     </row>
     <row r="127">
@@ -29020,7 +29020,11 @@
           <t>Dividends paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MG.xlsx
+++ b/output/pdf_financials_xlsx/MG.xlsx
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>-328</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>0</v>
@@ -1874,10 +1874,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C23" s="3" t="n">
+        <v>71</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-453</v>
@@ -6876,10 +6874,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C99" s="3" t="n">
+        <v>71</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-453</v>
@@ -8227,55 +8223,55 @@
         <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-247</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-407</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-1020</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-1783</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-515</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-904</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-1271</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-1831</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-1289</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-517</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-780</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="R121" s="3" t="n">
-        <v>0</v>
+        <v>-207</v>
       </c>
       <c r="S121" s="3" t="n">
-        <v>0</v>
+        <v>-137</v>
       </c>
     </row>
     <row r="122">
@@ -9197,7 +9193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V428"/>
+  <dimension ref="A1:V484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -28832,7 +28828,11 @@
           <t>Repurchase of Common Shares 21</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -30160,7 +30160,11 @@
           <t>Repurchase of Common Shares 20</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -31886,7 +31890,11 @@
           <t>Repurchase of Common Shares 17</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -33980,7 +33988,11 @@
           <t>Repurchase of Common Shares 19</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -37602,7 +37614,11 @@
           <t>Repurchase of Common Shares 18</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -37810,7 +37826,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -52352,12 +52372,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>reimbursement for any shortfall will be made annually.</t>
+          <t>Adoption of United States Generally Accepted Accounting Principles</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>harmonized our Canadian and U.S. GAAP reporting for such arrangements. For separately priced in-house tooling and engineering services contracts provided in conjunction with subsequent production or assembly services entered into prior to January</t>
+          <t>Reporting Standards ("IFRS") for all publicly accountable entities no later than fiscal years commencing on or after January</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
@@ -52366,18 +52386,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F426" s="5" t="n">
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G426" s="5" t="n">
+        <v>2011</v>
+      </c>
+      <c r="H426" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
@@ -52458,12 +52476,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>obligations and future expense.</t>
+          <t>COMMITMENTS AND CONTINGENCIES</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>costs and retirement medical benefit expense in 2009 and future years. As a result of amending the plan, a curtailment gain of $26 million was recorded in cost of goods sold in the second quarter of</t>
+          <t>For a discussion of risk factors relating to legal and other claims against us, refer to "Item 3. Description of the Business - Risk Factors" in our Annual Information Form and Annual Report on Form 40-F, each in respect of the year ended December</t>
         </is>
       </c>
       <c r="D427" t="inlineStr"/>
@@ -52472,18 +52490,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F427" s="5" t="n">
-        <v>2009</v>
-      </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G427" s="5" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H427" s="5" t="n">
+        <v>31</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
@@ -52564,12 +52580,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>FUTURE CHANGES IN ACCOUNTING POLICIES</t>
+          <t>within the time periods specified under applicable law.</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Conversion to International Financial Reporting Standards ("IFRS") in Fiscal</t>
+          <t>2010, such internal control over financial reporting is effective and that there were no material weaknesses. Our independent auditor, audited consolidated financial statements for the year ended December</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
@@ -52578,85 +52594,5987 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F428" s="5" t="n">
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G428" s="5" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H428" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>and Comprehensive Income (Loss)</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Sales $ 24,102 $</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G429" s="5" t="n">
+        <v>23704</v>
+      </c>
+      <c r="H429" s="5" t="n">
+        <v>17367</v>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Costs and expenses</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Cost of goods sold 5, 17 20,924</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G430" s="5" t="n">
+        <v>20982</v>
+      </c>
+      <c r="H430" s="5" t="n">
+        <v>15697</v>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Costs and expenses</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization 661</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G431" s="5" t="n">
+        <v>873</v>
+      </c>
+      <c r="H431" s="5" t="n">
+        <v>737</v>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Costs and expenses</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Selling, general and administrative 5, 10, 18, 21 1,340</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G432" s="5" t="n">
+        <v>1319</v>
+      </c>
+      <c r="H432" s="5" t="n">
+        <v>1261</v>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Costs and expenses</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Interest (income) expense, net 16 (10)</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr"/>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G433" s="5" t="n">
+        <v>-62</v>
+      </c>
+      <c r="H433" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Costs and expenses</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Equity income (33)</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G434" s="5" t="n">
+        <v>-19</v>
+      </c>
+      <c r="H434" s="5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Costs and expenses</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Impairment charges 5 23</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr"/>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G435" s="5" t="n">
+        <v>283</v>
+      </c>
+      <c r="H435" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Income (loss) from operations before income taxes</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Income (loss) from operations before income taxes and minority interest 1,197</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G436" s="5" t="n">
+        <v>-328</v>
+      </c>
+      <c r="H436" s="5" t="n">
+        <v>511</v>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Income (loss) from operations before income taxes</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Income taxes 13 236</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G437" s="5" t="n">
+        <v>257</v>
+      </c>
+      <c r="H437" s="5" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Income (loss) from operations before income taxes</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Minority interest (12)</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Income (loss) from operations before income taxes</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Net income (loss) 973</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G439" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="H439" s="5" t="n">
+        <v>-493</v>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Net realized and unrealized gains (losses) on translation</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Net realized and unrealized gains (losses) on translation of net investment in foreign operations 18</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr"/>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G440" s="5" t="n">
+        <v>-881</v>
+      </c>
+      <c r="H440" s="5" t="n">
+        <v>407</v>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Net realized and unrealized gains (losses) on translation</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Repurchase of shares 19 (3)</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr"/>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G441" s="5" t="n">
+        <v>-32</v>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Net realized and unrealized gains (losses) on translation</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Net unrealized gains (losses) on cash flow hedges 81</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr"/>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G442" s="5" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H442" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Net realized and unrealized gains (losses) on translation</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Reclassification of net (gains) losses on cash flow hedges to net income (loss) (28)</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr"/>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G443" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H443" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Net realized and unrealized gains (losses) on translation</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Net unrealized gains on available-for-sale investments 11</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr"/>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Net realized and unrealized gains (losses) on translation</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Comprehensive income (loss) $ 1,052 $</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr"/>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G445" s="5" t="n">
+        <v>-945</v>
+      </c>
+      <c r="H445" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>[restated - note 3]                                            6</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Basic $ 4.23 $</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr"/>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G446" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H446" s="5" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>[restated - note 3]                                            6</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Diluted $ 4.18 $</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr"/>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G447" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H447" s="5" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>[restated - note 3]                                            6</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>[restated - note 3] $ 0.42 $</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr"/>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G448" s="5" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H448" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>[restated - note 3]:                                            6</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Basic 230.0</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr"/>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G449" s="5" t="n">
+        <v>225.6</v>
+      </c>
+      <c r="H449" s="5" t="n">
+        <v>223.6</v>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>[restated - note 3]:                                            6</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Diluted 233.0</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr"/>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G450" s="5" t="n">
+        <v>227.8</v>
+      </c>
+      <c r="H450" s="5" t="n">
+        <v>223.6</v>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>MAGNA INTERNATIONAL INC.</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Retained earnings, beginning of year $ 2,843 $</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr"/>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G451" s="5" t="n">
+        <v>3526</v>
+      </c>
+      <c r="H451" s="5" t="n">
+        <v>3357</v>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>MAGNA INTERNATIONAL INC.</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Net income (loss) 973</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G452" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="H452" s="5" t="n">
+        <v>-493</v>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>MAGNA INTERNATIONAL INC.</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Dividends on Common Shares and Class B Shares (102)</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr"/>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G453" s="5" t="n">
+        <v>-142</v>
+      </c>
+      <c r="H453" s="5" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>MAGNA INTERNATIONAL INC.</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Repurchase of Class B Shares 4, 19 (976)</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr"/>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>MAGNA INTERNATIONAL INC.</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Repurchase of Common Shares 19 (13)</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr"/>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G455" s="5" t="n">
+        <v>-98</v>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>MAGNA INTERNATIONAL INC.</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Retained earnings, end of year $ 2,725 $</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr"/>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G456" s="5" t="n">
+        <v>3357</v>
+      </c>
+      <c r="H456" s="5" t="n">
+        <v>2843</v>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Net income (loss) $ 973 $</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G457" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="H457" s="5" t="n">
+        <v>-493</v>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Items not involving current cash flows 7 722</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr"/>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G458" s="5" t="n">
+        <v>1258</v>
+      </c>
+      <c r="H458" s="5" t="n">
+        <v>1114</v>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES total</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr"/>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G459" s="5" t="n">
+        <v>1329</v>
+      </c>
+      <c r="H459" s="5" t="n">
+        <v>621</v>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Changes in non-cash operating assets and liabilities 7 177</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr"/>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G460" s="5" t="n">
+        <v>-275</v>
+      </c>
+      <c r="H460" s="5" t="n">
+        <v>-94</v>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Cash provided from operating activities 1,872</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr"/>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G461" s="5" t="n">
+        <v>1054</v>
+      </c>
+      <c r="H461" s="5" t="n">
+        <v>527</v>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>INVESTMENT ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Fixed asset additions (784)</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr"/>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G462" s="5" t="n">
+        <v>-739</v>
+      </c>
+      <c r="H462" s="5" t="n">
+        <v>-629</v>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>INVESTMENT ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Purchase of subsidiaries 8 (106)</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr"/>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G463" s="5" t="n">
+        <v>-158</v>
+      </c>
+      <c r="H463" s="5" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>INVESTMENT ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Increase in investments and other assets (141)</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr"/>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G464" s="5" t="n">
+        <v>-231</v>
+      </c>
+      <c r="H464" s="5" t="n">
+        <v>-227</v>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>INVESTMENT ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Proceeds from disposition 287</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr"/>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G465" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="H465" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>INVESTMENT ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Cash used for investment activities (744)</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr"/>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G466" s="5" t="n">
+        <v>-1063</v>
+      </c>
+      <c r="H466" s="5" t="n">
+        <v>-876</v>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>(Decrease) increase in bank indebtedness (4)</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr"/>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G467" s="5" t="n">
+        <v>827</v>
+      </c>
+      <c r="H467" s="5" t="n">
+        <v>-853</v>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Repayments of debt 16 (67)</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr"/>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G468" s="5" t="n">
+        <v>-354</v>
+      </c>
+      <c r="H468" s="5" t="n">
+        <v>-296</v>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Issues of debt 16 22</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr"/>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G469" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H469" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Issue of general partnership units by subsidiary 4 80</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr"/>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Issues of Common Shares 19 49</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr"/>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H471" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Settlement of stock appreciation rights 18 –</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr"/>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H472" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Settlement of stock options 18 (12)</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr"/>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Repurchase of Common Shares 19 (23)</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr"/>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G474" s="5" t="n">
+        <v>-247</v>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Repurchase of Class B Shares 4, 19 (300)</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr"/>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Dividends (100)</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr"/>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G476" s="5" t="n">
+        <v>-140</v>
+      </c>
+      <c r="H476" s="5" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Cash (used for) provided from financing activities (355)</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr"/>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G477" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="H477" s="5" t="n">
+        <v>-1164</v>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Effect of exchange rate changes on cash and cash equivalents (2)</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr"/>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G478" s="5" t="n">
+        <v>-277</v>
+      </c>
+      <c r="H478" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Net increase (decrease) in cash and cash equivalents during the year 771</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr"/>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G479" s="5" t="n">
+        <v>-197</v>
+      </c>
+      <c r="H479" s="5" t="n">
+        <v>-1423</v>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents, beginning of year 1,334</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr"/>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G480" s="5" t="n">
+        <v>2954</v>
+      </c>
+      <c r="H480" s="5" t="n">
+        <v>2757</v>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents, end of year $ 2,105 $</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr"/>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G481" s="5" t="n">
+        <v>2757</v>
+      </c>
+      <c r="H481" s="5" t="n">
+        <v>1334</v>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>reimbursement for any shortfall will be made annually.</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>harmonized our Canadian and U.S. GAAP reporting for such arrangements. For separately priced in-house tooling and engineering services contracts provided in conjunction with subsequent production or assembly services entered into prior to January</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr"/>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F482" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>obligations and future expense.</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>costs and retirement medical benefit expense in 2009 and future years. As a result of amending the plan, a curtailment gain of $26 million was recorded in cost of goods sold in the second quarter of</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr"/>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F483" s="5" t="n">
+        <v>2009</v>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>FUTURE CHANGES IN ACCOUNTING POLICIES</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Conversion to International Financial Reporting Standards ("IFRS") in Fiscal</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr"/>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F484" s="5" t="n">
         <v>2011</v>
       </c>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V428" t="inlineStr">
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V484" t="inlineStr">
         <is>
           <t>-</t>
         </is>
